--- a/01_INPUTS/Stock/stock.xlsx
+++ b/01_INPUTS/Stock/stock.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25601"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F39938D3-33A4-4F30-BE5F-FBED9EE62B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7ADBCD2D-50F4-4714-8040-D84868D9B0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11105" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10718" uniqueCount="816">
   <si>
     <t>Codigo</t>
   </si>
@@ -2546,8 +2546,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1" displayName="Table1" ref="A1:L999">
-  <autoFilter ref="A1:L999" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1" displayName="Table1" ref="A1:L956">
+  <autoFilter ref="A1:L956" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CodigoReparto" totalsRowLabel="Total"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="CodigoItem"/>
@@ -3217,7 +3217,7 @@
         <v>24</v>
       </c>
       <c r="I6">
-        <v>2412</v>
+        <v>2400</v>
       </c>
       <c r="J6">
         <v>2430</v>
@@ -3226,13 +3226,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>2412</v>
+        <v>2400</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -4225,22 +4225,22 @@
         <v>24</v>
       </c>
       <c r="I24">
-        <v>1370</v>
+        <v>1004</v>
       </c>
       <c r="J24">
-        <v>1460</v>
+        <v>1100</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>1370</v>
+        <v>1004</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -4281,22 +4281,22 @@
         <v>24</v>
       </c>
       <c r="I25">
-        <v>4027</v>
+        <v>3661</v>
       </c>
       <c r="J25">
-        <v>4243</v>
+        <v>3883</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>4027</v>
+        <v>3661</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -5121,16 +5121,16 @@
         <v>24</v>
       </c>
       <c r="I40">
-        <v>1077</v>
+        <v>717</v>
       </c>
       <c r="J40">
-        <v>1179</v>
+        <v>819</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>1077</v>
+        <v>717</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -5401,7 +5401,7 @@
         <v>24</v>
       </c>
       <c r="I45">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="J45">
         <v>262</v>
@@ -5410,13 +5410,13 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="M45">
         <v>0</v>
       </c>
       <c r="N45">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -5457,7 +5457,7 @@
         <v>24</v>
       </c>
       <c r="I46">
-        <v>4683</v>
+        <v>4647</v>
       </c>
       <c r="J46">
         <v>4683</v>
@@ -5466,19 +5466,19 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>4683</v>
+        <v>4647</v>
       </c>
       <c r="M46">
         <v>0</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>3726</v>
+        <v>96</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -5513,7 +5513,7 @@
         <v>24</v>
       </c>
       <c r="I47">
-        <v>2079</v>
+        <v>2049</v>
       </c>
       <c r="J47">
         <v>2121</v>
@@ -5522,19 +5522,19 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>2079</v>
+        <v>2049</v>
       </c>
       <c r="M47">
         <v>0</v>
       </c>
       <c r="N47">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>3918</v>
+        <v>306</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -12009,7 +12009,7 @@
         <v>24</v>
       </c>
       <c r="I163">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="J163">
         <v>171</v>
@@ -12018,13 +12018,13 @@
         <v>0</v>
       </c>
       <c r="L163">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="M163">
         <v>0</v>
       </c>
       <c r="N163">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O163">
         <v>0</v>
@@ -12065,7 +12065,7 @@
         <v>24</v>
       </c>
       <c r="I164">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="J164">
         <v>186</v>
@@ -12074,13 +12074,13 @@
         <v>0</v>
       </c>
       <c r="L164">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="M164">
         <v>0</v>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O164">
         <v>0</v>
@@ -12737,7 +12737,7 @@
         <v>24</v>
       </c>
       <c r="I176">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="J176">
         <v>428</v>
@@ -12746,13 +12746,13 @@
         <v>0</v>
       </c>
       <c r="L176">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="M176">
         <v>0</v>
       </c>
       <c r="N176">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O176">
         <v>0</v>
@@ -14240,7 +14240,7 @@
         <v>24</v>
       </c>
       <c r="I203">
-        <v>1725</v>
+        <v>1719</v>
       </c>
       <c r="J203">
         <v>1725</v>
@@ -14249,13 +14249,13 @@
         <v>0</v>
       </c>
       <c r="L203">
-        <v>1725</v>
+        <v>1719</v>
       </c>
       <c r="M203">
         <v>0</v>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O203">
         <v>0</v>
@@ -14744,7 +14744,7 @@
         <v>24</v>
       </c>
       <c r="I212">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="J212">
         <v>768</v>
@@ -14753,13 +14753,13 @@
         <v>0</v>
       </c>
       <c r="L212">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="M212">
         <v>0</v>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -14856,7 +14856,7 @@
         <v>24</v>
       </c>
       <c r="I214">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="J214">
         <v>408</v>
@@ -14865,13 +14865,13 @@
         <v>0</v>
       </c>
       <c r="L214">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="M214">
         <v>0</v>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O214">
         <v>0</v>
@@ -15976,7 +15976,7 @@
         <v>24</v>
       </c>
       <c r="I234">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="J234">
         <v>432</v>
@@ -15985,13 +15985,13 @@
         <v>0</v>
       </c>
       <c r="L234">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="M234">
         <v>0</v>
       </c>
       <c r="N234">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="O234">
         <v>0</v>
@@ -16017,7 +16017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L999"/>
+  <dimension ref="A1:L956"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -48105,16 +48105,16 @@
     </row>
     <row r="845" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A845">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B845" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C845" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="D845" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E845" t="s">
         <v>499</v>
@@ -48132,27 +48132,27 @@
         <v>24</v>
       </c>
       <c r="J845">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K845">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L845" t="s">
-        <v>526</v>
+        <v>25</v>
       </c>
     </row>
     <row r="846" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A846">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B846" t="s">
-        <v>715</v>
+        <v>522</v>
       </c>
       <c r="C846" t="s">
-        <v>716</v>
+        <v>523</v>
       </c>
       <c r="D846" t="s">
-        <v>715</v>
+        <v>522</v>
       </c>
       <c r="E846" t="s">
         <v>499</v>
@@ -48170,27 +48170,27 @@
         <v>24</v>
       </c>
       <c r="J846">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K846">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L846" t="s">
-        <v>662</v>
+        <v>25</v>
       </c>
     </row>
     <row r="847" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A847">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B847" t="s">
-        <v>545</v>
+        <v>426</v>
       </c>
       <c r="C847" t="s">
-        <v>546</v>
+        <v>427</v>
       </c>
       <c r="D847" t="s">
-        <v>545</v>
+        <v>426</v>
       </c>
       <c r="E847" t="s">
         <v>499</v>
@@ -48208,27 +48208,27 @@
         <v>24</v>
       </c>
       <c r="J847">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K847">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L847" t="s">
-        <v>547</v>
+        <v>25</v>
       </c>
     </row>
     <row r="848" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A848">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B848" t="s">
-        <v>551</v>
+        <v>657</v>
       </c>
       <c r="C848" t="s">
-        <v>552</v>
+        <v>658</v>
       </c>
       <c r="D848" t="s">
-        <v>551</v>
+        <v>657</v>
       </c>
       <c r="E848" t="s">
         <v>499</v>
@@ -48249,24 +48249,24 @@
         <v>0</v>
       </c>
       <c r="K848">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L848" t="s">
-        <v>550</v>
+        <v>659</v>
       </c>
     </row>
     <row r="849" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A849">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B849" t="s">
-        <v>559</v>
+        <v>712</v>
       </c>
       <c r="C849" t="s">
-        <v>560</v>
+        <v>713</v>
       </c>
       <c r="D849" t="s">
-        <v>559</v>
+        <v>712</v>
       </c>
       <c r="E849" t="s">
         <v>499</v>
@@ -48287,24 +48287,24 @@
         <v>0</v>
       </c>
       <c r="K849">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L849" t="s">
-        <v>558</v>
+        <v>714</v>
       </c>
     </row>
     <row r="850" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A850">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B850" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
       <c r="C850" t="s">
-        <v>562</v>
+        <v>525</v>
       </c>
       <c r="D850" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
       <c r="E850" t="s">
         <v>499</v>
@@ -48325,24 +48325,24 @@
         <v>0</v>
       </c>
       <c r="K850">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L850" t="s">
-        <v>563</v>
+        <v>526</v>
       </c>
     </row>
     <row r="851" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A851">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B851" t="s">
-        <v>564</v>
+        <v>527</v>
       </c>
       <c r="C851" t="s">
-        <v>565</v>
+        <v>528</v>
       </c>
       <c r="D851" t="s">
-        <v>564</v>
+        <v>527</v>
       </c>
       <c r="E851" t="s">
         <v>499</v>
@@ -48363,24 +48363,24 @@
         <v>0</v>
       </c>
       <c r="K851">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L851" t="s">
-        <v>566</v>
+        <v>529</v>
       </c>
     </row>
     <row r="852" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A852">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B852" t="s">
-        <v>567</v>
+        <v>741</v>
       </c>
       <c r="C852" t="s">
-        <v>568</v>
+        <v>742</v>
       </c>
       <c r="D852" t="s">
-        <v>567</v>
+        <v>741</v>
       </c>
       <c r="E852" t="s">
         <v>499</v>
@@ -48401,24 +48401,24 @@
         <v>0</v>
       </c>
       <c r="K852">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L852" t="s">
-        <v>569</v>
+        <v>662</v>
       </c>
     </row>
     <row r="853" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A853">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B853" t="s">
-        <v>575</v>
+        <v>715</v>
       </c>
       <c r="C853" t="s">
-        <v>576</v>
+        <v>716</v>
       </c>
       <c r="D853" t="s">
-        <v>575</v>
+        <v>715</v>
       </c>
       <c r="E853" t="s">
         <v>499</v>
@@ -48439,24 +48439,24 @@
         <v>0</v>
       </c>
       <c r="K853">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L853" t="s">
-        <v>577</v>
+        <v>662</v>
       </c>
     </row>
     <row r="854" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A854">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B854" t="s">
-        <v>591</v>
+        <v>536</v>
       </c>
       <c r="C854" t="s">
-        <v>592</v>
+        <v>537</v>
       </c>
       <c r="D854" t="s">
-        <v>591</v>
+        <v>536</v>
       </c>
       <c r="E854" t="s">
         <v>499</v>
@@ -48477,24 +48477,24 @@
         <v>0</v>
       </c>
       <c r="K854">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L854" t="s">
-        <v>593</v>
+        <v>538</v>
       </c>
     </row>
     <row r="855" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A855">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B855" t="s">
-        <v>599</v>
+        <v>717</v>
       </c>
       <c r="C855" t="s">
-        <v>600</v>
+        <v>718</v>
       </c>
       <c r="D855" t="s">
-        <v>599</v>
+        <v>717</v>
       </c>
       <c r="E855" t="s">
         <v>499</v>
@@ -48512,27 +48512,27 @@
         <v>24</v>
       </c>
       <c r="J855">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K855">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L855" t="s">
-        <v>601</v>
+        <v>662</v>
       </c>
     </row>
     <row r="856" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A856">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B856" t="s">
-        <v>615</v>
+        <v>539</v>
       </c>
       <c r="C856" t="s">
-        <v>616</v>
+        <v>540</v>
       </c>
       <c r="D856" t="s">
-        <v>615</v>
+        <v>539</v>
       </c>
       <c r="E856" t="s">
         <v>499</v>
@@ -48553,24 +48553,24 @@
         <v>0</v>
       </c>
       <c r="K856">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L856" t="s">
-        <v>566</v>
+        <v>541</v>
       </c>
     </row>
     <row r="857" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A857">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B857" t="s">
-        <v>617</v>
+        <v>771</v>
       </c>
       <c r="C857" t="s">
-        <v>618</v>
+        <v>772</v>
       </c>
       <c r="D857" t="s">
-        <v>617</v>
+        <v>771</v>
       </c>
       <c r="E857" t="s">
         <v>499</v>
@@ -48591,24 +48591,24 @@
         <v>0</v>
       </c>
       <c r="K857">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L857" t="s">
-        <v>544</v>
+        <v>659</v>
       </c>
     </row>
     <row r="858" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A858">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B858" t="s">
-        <v>619</v>
+        <v>721</v>
       </c>
       <c r="C858" t="s">
-        <v>620</v>
+        <v>722</v>
       </c>
       <c r="D858" t="s">
-        <v>619</v>
+        <v>721</v>
       </c>
       <c r="E858" t="s">
         <v>499</v>
@@ -48632,21 +48632,21 @@
         <v>3</v>
       </c>
       <c r="L858" t="s">
-        <v>566</v>
+        <v>723</v>
       </c>
     </row>
     <row r="859" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A859">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B859" t="s">
-        <v>670</v>
+        <v>724</v>
       </c>
       <c r="C859" t="s">
-        <v>671</v>
+        <v>725</v>
       </c>
       <c r="D859" t="s">
-        <v>670</v>
+        <v>724</v>
       </c>
       <c r="E859" t="s">
         <v>499</v>
@@ -48667,24 +48667,24 @@
         <v>0</v>
       </c>
       <c r="K859">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L859" t="s">
-        <v>563</v>
+        <v>723</v>
       </c>
     </row>
     <row r="860" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A860">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B860" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="C860" t="s">
-        <v>521</v>
+        <v>546</v>
       </c>
       <c r="D860" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="E860" t="s">
         <v>499</v>
@@ -48702,27 +48702,27 @@
         <v>24</v>
       </c>
       <c r="J860">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K860">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L860" t="s">
-        <v>25</v>
+        <v>547</v>
       </c>
     </row>
     <row r="861" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A861">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B861" t="s">
-        <v>524</v>
+        <v>548</v>
       </c>
       <c r="C861" t="s">
-        <v>525</v>
+        <v>549</v>
       </c>
       <c r="D861" t="s">
-        <v>524</v>
+        <v>548</v>
       </c>
       <c r="E861" t="s">
         <v>499</v>
@@ -48740,27 +48740,27 @@
         <v>24</v>
       </c>
       <c r="J861">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K861">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="L861" t="s">
-        <v>526</v>
+        <v>550</v>
       </c>
     </row>
     <row r="862" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A862">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B862" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C862" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D862" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="E862" t="s">
         <v>499</v>
@@ -48781,24 +48781,24 @@
         <v>0</v>
       </c>
       <c r="K862">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="L862" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
     </row>
     <row r="863" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A863">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B863" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="C863" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="D863" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="E863" t="s">
         <v>499</v>
@@ -48819,24 +48819,24 @@
         <v>0</v>
       </c>
       <c r="K863">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L863" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
     </row>
     <row r="864" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A864">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B864" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="C864" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="D864" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="E864" t="s">
         <v>499</v>
@@ -48857,24 +48857,24 @@
         <v>0</v>
       </c>
       <c r="K864">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L864" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
     </row>
     <row r="865" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A865">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B865" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="C865" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D865" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="E865" t="s">
         <v>499</v>
@@ -48892,27 +48892,27 @@
         <v>24</v>
       </c>
       <c r="J865">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K865">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L865" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
     </row>
     <row r="866" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A866">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B866" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C866" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D866" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E866" t="s">
         <v>499</v>
@@ -48930,18 +48930,18 @@
         <v>24</v>
       </c>
       <c r="J866">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K866">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L866" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
     </row>
     <row r="867" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A867">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B867" t="s">
         <v>564</v>
@@ -48968,10 +48968,10 @@
         <v>24</v>
       </c>
       <c r="J867">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K867">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L867" t="s">
         <v>566</v>
@@ -48979,7 +48979,7 @@
     </row>
     <row r="868" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A868">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B868" t="s">
         <v>567</v>
@@ -49006,10 +49006,10 @@
         <v>24</v>
       </c>
       <c r="J868">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K868">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L868" t="s">
         <v>569</v>
@@ -49017,7 +49017,7 @@
     </row>
     <row r="869" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A869">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B869" t="s">
         <v>570</v>
@@ -49047,7 +49047,7 @@
         <v>1</v>
       </c>
       <c r="K869">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L869" t="s">
         <v>572</v>
@@ -49055,16 +49055,16 @@
     </row>
     <row r="870" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A870">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B870" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C870" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D870" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E870" t="s">
         <v>499</v>
@@ -49082,27 +49082,27 @@
         <v>24</v>
       </c>
       <c r="J870">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K870">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L870" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="871" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A871">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B871" t="s">
-        <v>591</v>
+        <v>665</v>
       </c>
       <c r="C871" t="s">
-        <v>592</v>
+        <v>666</v>
       </c>
       <c r="D871" t="s">
-        <v>591</v>
+        <v>665</v>
       </c>
       <c r="E871" t="s">
         <v>499</v>
@@ -49123,24 +49123,24 @@
         <v>0</v>
       </c>
       <c r="K871">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L871" t="s">
-        <v>593</v>
+        <v>667</v>
       </c>
     </row>
     <row r="872" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A872">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B872" t="s">
-        <v>728</v>
+        <v>575</v>
       </c>
       <c r="C872" t="s">
-        <v>729</v>
+        <v>576</v>
       </c>
       <c r="D872" t="s">
-        <v>728</v>
+        <v>575</v>
       </c>
       <c r="E872" t="s">
         <v>499</v>
@@ -49161,24 +49161,24 @@
         <v>0</v>
       </c>
       <c r="K872">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="L872" t="s">
-        <v>610</v>
+        <v>577</v>
       </c>
     </row>
     <row r="873" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A873">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B873" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="C873" t="s">
-        <v>600</v>
+        <v>579</v>
       </c>
       <c r="D873" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="E873" t="s">
         <v>499</v>
@@ -49196,27 +49196,27 @@
         <v>24</v>
       </c>
       <c r="J873">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K873">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L873" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
     </row>
     <row r="874" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A874">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B874" t="s">
-        <v>615</v>
+        <v>581</v>
       </c>
       <c r="C874" t="s">
-        <v>616</v>
+        <v>582</v>
       </c>
       <c r="D874" t="s">
-        <v>615</v>
+        <v>581</v>
       </c>
       <c r="E874" t="s">
         <v>499</v>
@@ -49237,24 +49237,24 @@
         <v>0</v>
       </c>
       <c r="K874">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L874" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
     </row>
     <row r="875" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A875">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B875" t="s">
-        <v>617</v>
+        <v>583</v>
       </c>
       <c r="C875" t="s">
-        <v>618</v>
+        <v>584</v>
       </c>
       <c r="D875" t="s">
-        <v>617</v>
+        <v>583</v>
       </c>
       <c r="E875" t="s">
         <v>499</v>
@@ -49275,24 +49275,24 @@
         <v>0</v>
       </c>
       <c r="K875">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L875" t="s">
-        <v>544</v>
+        <v>585</v>
       </c>
     </row>
     <row r="876" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A876">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B876" t="s">
-        <v>619</v>
+        <v>586</v>
       </c>
       <c r="C876" t="s">
-        <v>620</v>
+        <v>587</v>
       </c>
       <c r="D876" t="s">
-        <v>619</v>
+        <v>586</v>
       </c>
       <c r="E876" t="s">
         <v>499</v>
@@ -49313,24 +49313,24 @@
         <v>0</v>
       </c>
       <c r="K876">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L876" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
     </row>
     <row r="877" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A877">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B877" t="s">
-        <v>670</v>
+        <v>591</v>
       </c>
       <c r="C877" t="s">
-        <v>671</v>
+        <v>592</v>
       </c>
       <c r="D877" t="s">
-        <v>670</v>
+        <v>591</v>
       </c>
       <c r="E877" t="s">
         <v>499</v>
@@ -49348,13 +49348,13 @@
         <v>24</v>
       </c>
       <c r="J877">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K877">
         <v>10</v>
       </c>
       <c r="L877" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
     </row>
     <row r="878" spans="1:12" x14ac:dyDescent="0.25">
@@ -49362,13 +49362,13 @@
         <v>4603</v>
       </c>
       <c r="B878" t="s">
-        <v>520</v>
+        <v>728</v>
       </c>
       <c r="C878" t="s">
-        <v>521</v>
+        <v>729</v>
       </c>
       <c r="D878" t="s">
-        <v>520</v>
+        <v>728</v>
       </c>
       <c r="E878" t="s">
         <v>499</v>
@@ -49386,13 +49386,13 @@
         <v>24</v>
       </c>
       <c r="J878">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K878">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L878" t="s">
-        <v>25</v>
+        <v>610</v>
       </c>
     </row>
     <row r="879" spans="1:12" x14ac:dyDescent="0.25">
@@ -49400,13 +49400,13 @@
         <v>4603</v>
       </c>
       <c r="B879" t="s">
-        <v>522</v>
+        <v>594</v>
       </c>
       <c r="C879" t="s">
-        <v>523</v>
+        <v>595</v>
       </c>
       <c r="D879" t="s">
-        <v>522</v>
+        <v>594</v>
       </c>
       <c r="E879" t="s">
         <v>499</v>
@@ -49424,13 +49424,13 @@
         <v>24</v>
       </c>
       <c r="J879">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K879">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L879" t="s">
-        <v>25</v>
+        <v>596</v>
       </c>
     </row>
     <row r="880" spans="1:12" x14ac:dyDescent="0.25">
@@ -49438,13 +49438,13 @@
         <v>4603</v>
       </c>
       <c r="B880" t="s">
-        <v>426</v>
+        <v>599</v>
       </c>
       <c r="C880" t="s">
-        <v>427</v>
+        <v>600</v>
       </c>
       <c r="D880" t="s">
-        <v>426</v>
+        <v>599</v>
       </c>
       <c r="E880" t="s">
         <v>499</v>
@@ -49462,13 +49462,13 @@
         <v>24</v>
       </c>
       <c r="J880">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K880">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L880" t="s">
-        <v>25</v>
+        <v>601</v>
       </c>
     </row>
     <row r="881" spans="1:12" x14ac:dyDescent="0.25">
@@ -49476,13 +49476,13 @@
         <v>4603</v>
       </c>
       <c r="B881" t="s">
-        <v>657</v>
+        <v>780</v>
       </c>
       <c r="C881" t="s">
-        <v>658</v>
+        <v>781</v>
       </c>
       <c r="D881" t="s">
-        <v>657</v>
+        <v>780</v>
       </c>
       <c r="E881" t="s">
         <v>499</v>
@@ -49503,10 +49503,10 @@
         <v>0</v>
       </c>
       <c r="K881">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L881" t="s">
-        <v>659</v>
+        <v>566</v>
       </c>
     </row>
     <row r="882" spans="1:12" x14ac:dyDescent="0.25">
@@ -49514,13 +49514,13 @@
         <v>4603</v>
       </c>
       <c r="B882" t="s">
-        <v>712</v>
+        <v>668</v>
       </c>
       <c r="C882" t="s">
-        <v>713</v>
+        <v>669</v>
       </c>
       <c r="D882" t="s">
-        <v>712</v>
+        <v>668</v>
       </c>
       <c r="E882" t="s">
         <v>499</v>
@@ -49544,7 +49544,7 @@
         <v>5</v>
       </c>
       <c r="L882" t="s">
-        <v>714</v>
+        <v>566</v>
       </c>
     </row>
     <row r="883" spans="1:12" x14ac:dyDescent="0.25">
@@ -49552,13 +49552,13 @@
         <v>4603</v>
       </c>
       <c r="B883" t="s">
-        <v>524</v>
+        <v>606</v>
       </c>
       <c r="C883" t="s">
-        <v>525</v>
+        <v>607</v>
       </c>
       <c r="D883" t="s">
-        <v>524</v>
+        <v>606</v>
       </c>
       <c r="E883" t="s">
         <v>499</v>
@@ -49579,10 +49579,10 @@
         <v>0</v>
       </c>
       <c r="K883">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L883" t="s">
-        <v>526</v>
+        <v>593</v>
       </c>
     </row>
     <row r="884" spans="1:12" x14ac:dyDescent="0.25">
@@ -49590,13 +49590,13 @@
         <v>4603</v>
       </c>
       <c r="B884" t="s">
-        <v>527</v>
+        <v>611</v>
       </c>
       <c r="C884" t="s">
-        <v>528</v>
+        <v>612</v>
       </c>
       <c r="D884" t="s">
-        <v>527</v>
+        <v>611</v>
       </c>
       <c r="E884" t="s">
         <v>499</v>
@@ -49617,10 +49617,10 @@
         <v>0</v>
       </c>
       <c r="K884">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L884" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
     </row>
     <row r="885" spans="1:12" x14ac:dyDescent="0.25">
@@ -49628,13 +49628,13 @@
         <v>4603</v>
       </c>
       <c r="B885" t="s">
-        <v>741</v>
+        <v>613</v>
       </c>
       <c r="C885" t="s">
-        <v>742</v>
+        <v>614</v>
       </c>
       <c r="D885" t="s">
-        <v>741</v>
+        <v>613</v>
       </c>
       <c r="E885" t="s">
         <v>499</v>
@@ -49655,10 +49655,10 @@
         <v>0</v>
       </c>
       <c r="K885">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L885" t="s">
-        <v>662</v>
+        <v>566</v>
       </c>
     </row>
     <row r="886" spans="1:12" x14ac:dyDescent="0.25">
@@ -49666,13 +49666,13 @@
         <v>4603</v>
       </c>
       <c r="B886" t="s">
-        <v>715</v>
+        <v>615</v>
       </c>
       <c r="C886" t="s">
-        <v>716</v>
+        <v>616</v>
       </c>
       <c r="D886" t="s">
-        <v>715</v>
+        <v>615</v>
       </c>
       <c r="E886" t="s">
         <v>499</v>
@@ -49693,10 +49693,10 @@
         <v>0</v>
       </c>
       <c r="K886">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="L886" t="s">
-        <v>662</v>
+        <v>566</v>
       </c>
     </row>
     <row r="887" spans="1:12" x14ac:dyDescent="0.25">
@@ -49704,13 +49704,13 @@
         <v>4603</v>
       </c>
       <c r="B887" t="s">
-        <v>536</v>
+        <v>617</v>
       </c>
       <c r="C887" t="s">
-        <v>537</v>
+        <v>618</v>
       </c>
       <c r="D887" t="s">
-        <v>536</v>
+        <v>617</v>
       </c>
       <c r="E887" t="s">
         <v>499</v>
@@ -49731,10 +49731,10 @@
         <v>0</v>
       </c>
       <c r="K887">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L887" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="888" spans="1:12" x14ac:dyDescent="0.25">
@@ -49742,13 +49742,13 @@
         <v>4603</v>
       </c>
       <c r="B888" t="s">
-        <v>717</v>
+        <v>813</v>
       </c>
       <c r="C888" t="s">
-        <v>718</v>
+        <v>814</v>
       </c>
       <c r="D888" t="s">
-        <v>717</v>
+        <v>813</v>
       </c>
       <c r="E888" t="s">
         <v>499</v>
@@ -49769,10 +49769,10 @@
         <v>0</v>
       </c>
       <c r="K888">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L888" t="s">
-        <v>662</v>
+        <v>815</v>
       </c>
     </row>
     <row r="889" spans="1:12" x14ac:dyDescent="0.25">
@@ -49780,13 +49780,13 @@
         <v>4603</v>
       </c>
       <c r="B889" t="s">
-        <v>539</v>
+        <v>619</v>
       </c>
       <c r="C889" t="s">
-        <v>540</v>
+        <v>620</v>
       </c>
       <c r="D889" t="s">
-        <v>539</v>
+        <v>619</v>
       </c>
       <c r="E889" t="s">
         <v>499</v>
@@ -49807,10 +49807,10 @@
         <v>0</v>
       </c>
       <c r="K889">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="L889" t="s">
-        <v>541</v>
+        <v>566</v>
       </c>
     </row>
     <row r="890" spans="1:12" x14ac:dyDescent="0.25">
@@ -49818,13 +49818,13 @@
         <v>4603</v>
       </c>
       <c r="B890" t="s">
-        <v>771</v>
+        <v>633</v>
       </c>
       <c r="C890" t="s">
-        <v>772</v>
+        <v>634</v>
       </c>
       <c r="D890" t="s">
-        <v>771</v>
+        <v>633</v>
       </c>
       <c r="E890" t="s">
         <v>499</v>
@@ -49848,7 +49848,7 @@
         <v>3</v>
       </c>
       <c r="L890" t="s">
-        <v>659</v>
+        <v>532</v>
       </c>
     </row>
     <row r="891" spans="1:12" x14ac:dyDescent="0.25">
@@ -49856,13 +49856,13 @@
         <v>4603</v>
       </c>
       <c r="B891" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="C891" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="D891" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="E891" t="s">
         <v>499</v>
@@ -49883,10 +49883,10 @@
         <v>0</v>
       </c>
       <c r="K891">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L891" t="s">
-        <v>723</v>
+        <v>572</v>
       </c>
     </row>
     <row r="892" spans="1:12" x14ac:dyDescent="0.25">
@@ -49894,13 +49894,13 @@
         <v>4603</v>
       </c>
       <c r="B892" t="s">
-        <v>724</v>
+        <v>670</v>
       </c>
       <c r="C892" t="s">
-        <v>725</v>
+        <v>671</v>
       </c>
       <c r="D892" t="s">
-        <v>724</v>
+        <v>670</v>
       </c>
       <c r="E892" t="s">
         <v>499</v>
@@ -49921,10 +49921,10 @@
         <v>0</v>
       </c>
       <c r="K892">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L892" t="s">
-        <v>723</v>
+        <v>563</v>
       </c>
     </row>
     <row r="893" spans="1:12" x14ac:dyDescent="0.25">
@@ -49932,13 +49932,13 @@
         <v>4603</v>
       </c>
       <c r="B893" t="s">
-        <v>545</v>
+        <v>635</v>
       </c>
       <c r="C893" t="s">
-        <v>546</v>
+        <v>636</v>
       </c>
       <c r="D893" t="s">
-        <v>545</v>
+        <v>635</v>
       </c>
       <c r="E893" t="s">
         <v>499</v>
@@ -49959,10 +49959,10 @@
         <v>0</v>
       </c>
       <c r="K893">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L893" t="s">
-        <v>547</v>
+        <v>577</v>
       </c>
     </row>
     <row r="894" spans="1:12" x14ac:dyDescent="0.25">
@@ -49970,13 +49970,13 @@
         <v>4603</v>
       </c>
       <c r="B894" t="s">
-        <v>548</v>
+        <v>672</v>
       </c>
       <c r="C894" t="s">
-        <v>549</v>
+        <v>673</v>
       </c>
       <c r="D894" t="s">
-        <v>548</v>
+        <v>672</v>
       </c>
       <c r="E894" t="s">
         <v>499</v>
@@ -49997,10 +49997,10 @@
         <v>0</v>
       </c>
       <c r="K894">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="L894" t="s">
-        <v>550</v>
+        <v>674</v>
       </c>
     </row>
     <row r="895" spans="1:12" x14ac:dyDescent="0.25">
@@ -50008,13 +50008,13 @@
         <v>4603</v>
       </c>
       <c r="B895" t="s">
-        <v>551</v>
+        <v>646</v>
       </c>
       <c r="C895" t="s">
-        <v>552</v>
+        <v>647</v>
       </c>
       <c r="D895" t="s">
-        <v>551</v>
+        <v>646</v>
       </c>
       <c r="E895" t="s">
         <v>499</v>
@@ -50035,10 +50035,10 @@
         <v>0</v>
       </c>
       <c r="K895">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="L895" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
     </row>
     <row r="896" spans="1:12" x14ac:dyDescent="0.25">
@@ -50046,13 +50046,13 @@
         <v>4603</v>
       </c>
       <c r="B896" t="s">
-        <v>553</v>
+        <v>648</v>
       </c>
       <c r="C896" t="s">
-        <v>554</v>
+        <v>649</v>
       </c>
       <c r="D896" t="s">
-        <v>553</v>
+        <v>648</v>
       </c>
       <c r="E896" t="s">
         <v>499</v>
@@ -50073,10 +50073,10 @@
         <v>0</v>
       </c>
       <c r="K896">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L896" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="897" spans="1:12" x14ac:dyDescent="0.25">
@@ -50084,13 +50084,13 @@
         <v>4603</v>
       </c>
       <c r="B897" t="s">
-        <v>556</v>
+        <v>68</v>
       </c>
       <c r="C897" t="s">
-        <v>557</v>
+        <v>69</v>
       </c>
       <c r="D897" t="s">
-        <v>556</v>
+        <v>68</v>
       </c>
       <c r="E897" t="s">
         <v>499</v>
@@ -50108,13 +50108,13 @@
         <v>24</v>
       </c>
       <c r="J897">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K897">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L897" t="s">
-        <v>558</v>
+        <v>25</v>
       </c>
     </row>
     <row r="898" spans="1:12" x14ac:dyDescent="0.25">
@@ -50122,13 +50122,13 @@
         <v>4603</v>
       </c>
       <c r="B898" t="s">
-        <v>559</v>
+        <v>70</v>
       </c>
       <c r="C898" t="s">
-        <v>560</v>
+        <v>71</v>
       </c>
       <c r="D898" t="s">
-        <v>559</v>
+        <v>70</v>
       </c>
       <c r="E898" t="s">
         <v>499</v>
@@ -50146,13 +50146,13 @@
         <v>24</v>
       </c>
       <c r="J898">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K898">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L898" t="s">
-        <v>558</v>
+        <v>25</v>
       </c>
     </row>
     <row r="899" spans="1:12" x14ac:dyDescent="0.25">
@@ -50160,13 +50160,13 @@
         <v>4603</v>
       </c>
       <c r="B899" t="s">
-        <v>561</v>
+        <v>100</v>
       </c>
       <c r="C899" t="s">
-        <v>562</v>
+        <v>101</v>
       </c>
       <c r="D899" t="s">
-        <v>561</v>
+        <v>100</v>
       </c>
       <c r="E899" t="s">
         <v>499</v>
@@ -50184,13 +50184,13 @@
         <v>24</v>
       </c>
       <c r="J899">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K899">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L899" t="s">
-        <v>563</v>
+        <v>25</v>
       </c>
     </row>
     <row r="900" spans="1:12" x14ac:dyDescent="0.25">
@@ -50198,13 +50198,13 @@
         <v>4603</v>
       </c>
       <c r="B900" t="s">
-        <v>564</v>
+        <v>373</v>
       </c>
       <c r="C900" t="s">
-        <v>565</v>
+        <v>374</v>
       </c>
       <c r="D900" t="s">
-        <v>564</v>
+        <v>373</v>
       </c>
       <c r="E900" t="s">
         <v>499</v>
@@ -50222,13 +50222,13 @@
         <v>24</v>
       </c>
       <c r="J900">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K900">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L900" t="s">
-        <v>566</v>
+        <v>25</v>
       </c>
     </row>
     <row r="901" spans="1:12" x14ac:dyDescent="0.25">
@@ -50236,13 +50236,13 @@
         <v>4603</v>
       </c>
       <c r="B901" t="s">
-        <v>567</v>
+        <v>122</v>
       </c>
       <c r="C901" t="s">
-        <v>568</v>
+        <v>123</v>
       </c>
       <c r="D901" t="s">
-        <v>567</v>
+        <v>122</v>
       </c>
       <c r="E901" t="s">
         <v>499</v>
@@ -50260,13 +50260,13 @@
         <v>24</v>
       </c>
       <c r="J901">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K901">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L901" t="s">
-        <v>569</v>
+        <v>25</v>
       </c>
     </row>
     <row r="902" spans="1:12" x14ac:dyDescent="0.25">
@@ -50274,13 +50274,13 @@
         <v>4603</v>
       </c>
       <c r="B902" t="s">
-        <v>570</v>
+        <v>180</v>
       </c>
       <c r="C902" t="s">
-        <v>571</v>
+        <v>181</v>
       </c>
       <c r="D902" t="s">
-        <v>570</v>
+        <v>180</v>
       </c>
       <c r="E902" t="s">
         <v>499</v>
@@ -50298,13 +50298,13 @@
         <v>24</v>
       </c>
       <c r="J902">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K902">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L902" t="s">
-        <v>572</v>
+        <v>25</v>
       </c>
     </row>
     <row r="903" spans="1:12" x14ac:dyDescent="0.25">
@@ -50312,13 +50312,13 @@
         <v>4603</v>
       </c>
       <c r="B903" t="s">
-        <v>573</v>
+        <v>202</v>
       </c>
       <c r="C903" t="s">
-        <v>574</v>
+        <v>203</v>
       </c>
       <c r="D903" t="s">
-        <v>573</v>
+        <v>202</v>
       </c>
       <c r="E903" t="s">
         <v>499</v>
@@ -50336,13 +50336,13 @@
         <v>24</v>
       </c>
       <c r="J903">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K903">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L903" t="s">
-        <v>572</v>
+        <v>25</v>
       </c>
     </row>
     <row r="904" spans="1:12" x14ac:dyDescent="0.25">
@@ -50350,13 +50350,13 @@
         <v>4603</v>
       </c>
       <c r="B904" t="s">
-        <v>665</v>
+        <v>204</v>
       </c>
       <c r="C904" t="s">
-        <v>666</v>
+        <v>205</v>
       </c>
       <c r="D904" t="s">
-        <v>665</v>
+        <v>204</v>
       </c>
       <c r="E904" t="s">
         <v>499</v>
@@ -50374,13 +50374,13 @@
         <v>24</v>
       </c>
       <c r="J904">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K904">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L904" t="s">
-        <v>667</v>
+        <v>25</v>
       </c>
     </row>
     <row r="905" spans="1:12" x14ac:dyDescent="0.25">
@@ -50388,13 +50388,13 @@
         <v>4603</v>
       </c>
       <c r="B905" t="s">
-        <v>575</v>
+        <v>240</v>
       </c>
       <c r="C905" t="s">
-        <v>576</v>
+        <v>241</v>
       </c>
       <c r="D905" t="s">
-        <v>575</v>
+        <v>240</v>
       </c>
       <c r="E905" t="s">
         <v>499</v>
@@ -50412,13 +50412,13 @@
         <v>24</v>
       </c>
       <c r="J905">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K905">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L905" t="s">
-        <v>577</v>
+        <v>25</v>
       </c>
     </row>
     <row r="906" spans="1:12" x14ac:dyDescent="0.25">
@@ -50426,13 +50426,13 @@
         <v>4603</v>
       </c>
       <c r="B906" t="s">
-        <v>578</v>
+        <v>257</v>
       </c>
       <c r="C906" t="s">
-        <v>579</v>
+        <v>258</v>
       </c>
       <c r="D906" t="s">
-        <v>578</v>
+        <v>257</v>
       </c>
       <c r="E906" t="s">
         <v>499</v>
@@ -50450,13 +50450,13 @@
         <v>24</v>
       </c>
       <c r="J906">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K906">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L906" t="s">
-        <v>580</v>
+        <v>25</v>
       </c>
     </row>
     <row r="907" spans="1:12" x14ac:dyDescent="0.25">
@@ -50464,13 +50464,13 @@
         <v>4603</v>
       </c>
       <c r="B907" t="s">
-        <v>581</v>
+        <v>273</v>
       </c>
       <c r="C907" t="s">
-        <v>582</v>
+        <v>274</v>
       </c>
       <c r="D907" t="s">
-        <v>581</v>
+        <v>273</v>
       </c>
       <c r="E907" t="s">
         <v>499</v>
@@ -50488,13 +50488,13 @@
         <v>24</v>
       </c>
       <c r="J907">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K907">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L907" t="s">
-        <v>580</v>
+        <v>25</v>
       </c>
     </row>
     <row r="908" spans="1:12" x14ac:dyDescent="0.25">
@@ -50502,13 +50502,13 @@
         <v>4603</v>
       </c>
       <c r="B908" t="s">
-        <v>583</v>
+        <v>297</v>
       </c>
       <c r="C908" t="s">
-        <v>584</v>
+        <v>298</v>
       </c>
       <c r="D908" t="s">
-        <v>583</v>
+        <v>297</v>
       </c>
       <c r="E908" t="s">
         <v>499</v>
@@ -50526,13 +50526,13 @@
         <v>24</v>
       </c>
       <c r="J908">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K908">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L908" t="s">
-        <v>585</v>
+        <v>25</v>
       </c>
     </row>
     <row r="909" spans="1:12" x14ac:dyDescent="0.25">
@@ -50540,13 +50540,13 @@
         <v>4603</v>
       </c>
       <c r="B909" t="s">
-        <v>586</v>
+        <v>367</v>
       </c>
       <c r="C909" t="s">
-        <v>587</v>
+        <v>368</v>
       </c>
       <c r="D909" t="s">
-        <v>586</v>
+        <v>367</v>
       </c>
       <c r="E909" t="s">
         <v>499</v>
@@ -50564,13 +50564,13 @@
         <v>24</v>
       </c>
       <c r="J909">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K909">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L909" t="s">
-        <v>585</v>
+        <v>25</v>
       </c>
     </row>
     <row r="910" spans="1:12" x14ac:dyDescent="0.25">
@@ -50578,13 +50578,13 @@
         <v>4603</v>
       </c>
       <c r="B910" t="s">
-        <v>591</v>
+        <v>307</v>
       </c>
       <c r="C910" t="s">
-        <v>592</v>
+        <v>308</v>
       </c>
       <c r="D910" t="s">
-        <v>591</v>
+        <v>307</v>
       </c>
       <c r="E910" t="s">
         <v>499</v>
@@ -50602,13 +50602,13 @@
         <v>24</v>
       </c>
       <c r="J910">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K910">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L910" t="s">
-        <v>593</v>
+        <v>25</v>
       </c>
     </row>
     <row r="911" spans="1:12" x14ac:dyDescent="0.25">
@@ -50616,13 +50616,13 @@
         <v>4603</v>
       </c>
       <c r="B911" t="s">
-        <v>728</v>
+        <v>311</v>
       </c>
       <c r="C911" t="s">
-        <v>729</v>
+        <v>312</v>
       </c>
       <c r="D911" t="s">
-        <v>728</v>
+        <v>311</v>
       </c>
       <c r="E911" t="s">
         <v>499</v>
@@ -50640,27 +50640,27 @@
         <v>24</v>
       </c>
       <c r="J911">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K911">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L911" t="s">
-        <v>610</v>
+        <v>25</v>
       </c>
     </row>
     <row r="912" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A912">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B912" t="s">
-        <v>594</v>
+        <v>32</v>
       </c>
       <c r="C912" t="s">
-        <v>595</v>
+        <v>33</v>
       </c>
       <c r="D912" t="s">
-        <v>594</v>
+        <v>32</v>
       </c>
       <c r="E912" t="s">
         <v>499</v>
@@ -50678,27 +50678,27 @@
         <v>24</v>
       </c>
       <c r="J912">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K912">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L912" t="s">
-        <v>596</v>
+        <v>25</v>
       </c>
     </row>
     <row r="913" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A913">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B913" t="s">
-        <v>599</v>
+        <v>426</v>
       </c>
       <c r="C913" t="s">
-        <v>600</v>
+        <v>427</v>
       </c>
       <c r="D913" t="s">
-        <v>599</v>
+        <v>426</v>
       </c>
       <c r="E913" t="s">
         <v>499</v>
@@ -50716,27 +50716,27 @@
         <v>24</v>
       </c>
       <c r="J913">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K913">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L913" t="s">
-        <v>601</v>
+        <v>25</v>
       </c>
     </row>
     <row r="914" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A914">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B914" t="s">
-        <v>780</v>
+        <v>52</v>
       </c>
       <c r="C914" t="s">
-        <v>781</v>
+        <v>53</v>
       </c>
       <c r="D914" t="s">
-        <v>780</v>
+        <v>52</v>
       </c>
       <c r="E914" t="s">
         <v>499</v>
@@ -50754,27 +50754,27 @@
         <v>24</v>
       </c>
       <c r="J914">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K914">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L914" t="s">
-        <v>566</v>
+        <v>25</v>
       </c>
     </row>
     <row r="915" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A915">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B915" t="s">
-        <v>668</v>
+        <v>60</v>
       </c>
       <c r="C915" t="s">
-        <v>669</v>
+        <v>61</v>
       </c>
       <c r="D915" t="s">
-        <v>668</v>
+        <v>60</v>
       </c>
       <c r="E915" t="s">
         <v>499</v>
@@ -50792,27 +50792,27 @@
         <v>24</v>
       </c>
       <c r="J915">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K915">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L915" t="s">
-        <v>566</v>
+        <v>25</v>
       </c>
     </row>
     <row r="916" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A916">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B916" t="s">
-        <v>606</v>
+        <v>567</v>
       </c>
       <c r="C916" t="s">
-        <v>607</v>
+        <v>568</v>
       </c>
       <c r="D916" t="s">
-        <v>606</v>
+        <v>567</v>
       </c>
       <c r="E916" t="s">
         <v>499</v>
@@ -50833,24 +50833,24 @@
         <v>0</v>
       </c>
       <c r="K916">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L916" t="s">
-        <v>593</v>
+        <v>569</v>
       </c>
     </row>
     <row r="917" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A917">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B917" t="s">
-        <v>611</v>
+        <v>578</v>
       </c>
       <c r="C917" t="s">
-        <v>612</v>
+        <v>579</v>
       </c>
       <c r="D917" t="s">
-        <v>611</v>
+        <v>578</v>
       </c>
       <c r="E917" t="s">
         <v>499</v>
@@ -50871,24 +50871,24 @@
         <v>0</v>
       </c>
       <c r="K917">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L917" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
     </row>
     <row r="918" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A918">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B918" t="s">
-        <v>613</v>
+        <v>581</v>
       </c>
       <c r="C918" t="s">
-        <v>614</v>
+        <v>582</v>
       </c>
       <c r="D918" t="s">
-        <v>613</v>
+        <v>581</v>
       </c>
       <c r="E918" t="s">
         <v>499</v>
@@ -50909,24 +50909,24 @@
         <v>0</v>
       </c>
       <c r="K918">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L918" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
     </row>
     <row r="919" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A919">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B919" t="s">
-        <v>615</v>
+        <v>583</v>
       </c>
       <c r="C919" t="s">
-        <v>616</v>
+        <v>584</v>
       </c>
       <c r="D919" t="s">
-        <v>615</v>
+        <v>583</v>
       </c>
       <c r="E919" t="s">
         <v>499</v>
@@ -50947,24 +50947,24 @@
         <v>0</v>
       </c>
       <c r="K919">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L919" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
     </row>
     <row r="920" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A920">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B920" t="s">
-        <v>617</v>
+        <v>586</v>
       </c>
       <c r="C920" t="s">
-        <v>618</v>
+        <v>587</v>
       </c>
       <c r="D920" t="s">
-        <v>617</v>
+        <v>586</v>
       </c>
       <c r="E920" t="s">
         <v>499</v>
@@ -50985,24 +50985,24 @@
         <v>0</v>
       </c>
       <c r="K920">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L920" t="s">
-        <v>544</v>
+        <v>585</v>
       </c>
     </row>
     <row r="921" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A921">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B921" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="C921" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D921" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="E921" t="s">
         <v>499</v>
@@ -51023,24 +51023,24 @@
         <v>0</v>
       </c>
       <c r="K921">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L921" t="s">
-        <v>815</v>
+        <v>566</v>
       </c>
     </row>
     <row r="922" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A922">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B922" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C922" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="D922" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="E922" t="s">
         <v>499</v>
@@ -51061,7 +51061,7 @@
         <v>0</v>
       </c>
       <c r="K922">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L922" t="s">
         <v>566</v>
@@ -51069,16 +51069,16 @@
     </row>
     <row r="923" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A923">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B923" t="s">
-        <v>633</v>
+        <v>613</v>
       </c>
       <c r="C923" t="s">
-        <v>634</v>
+        <v>614</v>
       </c>
       <c r="D923" t="s">
-        <v>633</v>
+        <v>613</v>
       </c>
       <c r="E923" t="s">
         <v>499</v>
@@ -51099,24 +51099,24 @@
         <v>0</v>
       </c>
       <c r="K923">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L923" t="s">
-        <v>532</v>
+        <v>566</v>
       </c>
     </row>
     <row r="924" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A924">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B924" t="s">
-        <v>730</v>
+        <v>615</v>
       </c>
       <c r="C924" t="s">
-        <v>731</v>
+        <v>616</v>
       </c>
       <c r="D924" t="s">
-        <v>730</v>
+        <v>615</v>
       </c>
       <c r="E924" t="s">
         <v>499</v>
@@ -51140,21 +51140,21 @@
         <v>8</v>
       </c>
       <c r="L924" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
     </row>
     <row r="925" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A925">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B925" t="s">
-        <v>670</v>
+        <v>637</v>
       </c>
       <c r="C925" t="s">
-        <v>671</v>
+        <v>638</v>
       </c>
       <c r="D925" t="s">
-        <v>670</v>
+        <v>637</v>
       </c>
       <c r="E925" t="s">
         <v>499</v>
@@ -51175,24 +51175,24 @@
         <v>0</v>
       </c>
       <c r="K925">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L925" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="926" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A926">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B926" t="s">
-        <v>635</v>
+        <v>66</v>
       </c>
       <c r="C926" t="s">
-        <v>636</v>
+        <v>67</v>
       </c>
       <c r="D926" t="s">
-        <v>635</v>
+        <v>66</v>
       </c>
       <c r="E926" t="s">
         <v>499</v>
@@ -51210,27 +51210,27 @@
         <v>24</v>
       </c>
       <c r="J926">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K926">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L926" t="s">
-        <v>577</v>
+        <v>25</v>
       </c>
     </row>
     <row r="927" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A927">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B927" t="s">
-        <v>672</v>
+        <v>68</v>
       </c>
       <c r="C927" t="s">
-        <v>673</v>
+        <v>69</v>
       </c>
       <c r="D927" t="s">
-        <v>672</v>
+        <v>68</v>
       </c>
       <c r="E927" t="s">
         <v>499</v>
@@ -51248,27 +51248,27 @@
         <v>24</v>
       </c>
       <c r="J927">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K927">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L927" t="s">
-        <v>674</v>
+        <v>25</v>
       </c>
     </row>
     <row r="928" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A928">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B928" t="s">
-        <v>646</v>
+        <v>70</v>
       </c>
       <c r="C928" t="s">
-        <v>647</v>
+        <v>71</v>
       </c>
       <c r="D928" t="s">
-        <v>646</v>
+        <v>70</v>
       </c>
       <c r="E928" t="s">
         <v>499</v>
@@ -51286,27 +51286,27 @@
         <v>24</v>
       </c>
       <c r="J928">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="K928">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L928" t="s">
-        <v>558</v>
+        <v>25</v>
       </c>
     </row>
     <row r="929" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A929">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B929" t="s">
-        <v>648</v>
+        <v>78</v>
       </c>
       <c r="C929" t="s">
-        <v>649</v>
+        <v>79</v>
       </c>
       <c r="D929" t="s">
-        <v>648</v>
+        <v>78</v>
       </c>
       <c r="E929" t="s">
         <v>499</v>
@@ -51324,27 +51324,27 @@
         <v>24</v>
       </c>
       <c r="J929">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K929">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L929" t="s">
-        <v>563</v>
+        <v>25</v>
       </c>
     </row>
     <row r="930" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A930">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B930" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C930" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="D930" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="E930" t="s">
         <v>499</v>
@@ -51362,7 +51362,7 @@
         <v>24</v>
       </c>
       <c r="J930">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="K930">
         <v>0</v>
@@ -51373,16 +51373,16 @@
     </row>
     <row r="931" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A931">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B931" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C931" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D931" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E931" t="s">
         <v>499</v>
@@ -51400,7 +51400,7 @@
         <v>24</v>
       </c>
       <c r="J931">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="K931">
         <v>0</v>
@@ -51411,16 +51411,16 @@
     </row>
     <row r="932" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A932">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B932" t="s">
-        <v>100</v>
+        <v>379</v>
       </c>
       <c r="C932" t="s">
-        <v>101</v>
+        <v>380</v>
       </c>
       <c r="D932" t="s">
-        <v>100</v>
+        <v>379</v>
       </c>
       <c r="E932" t="s">
         <v>499</v>
@@ -51438,7 +51438,7 @@
         <v>24</v>
       </c>
       <c r="J932">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K932">
         <v>0</v>
@@ -51449,16 +51449,16 @@
     </row>
     <row r="933" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A933">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B933" t="s">
-        <v>373</v>
+        <v>102</v>
       </c>
       <c r="C933" t="s">
-        <v>374</v>
+        <v>103</v>
       </c>
       <c r="D933" t="s">
-        <v>373</v>
+        <v>102</v>
       </c>
       <c r="E933" t="s">
         <v>499</v>
@@ -51476,7 +51476,7 @@
         <v>24</v>
       </c>
       <c r="J933">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K933">
         <v>0</v>
@@ -51487,16 +51487,16 @@
     </row>
     <row r="934" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A934">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B934" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C934" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D934" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="E934" t="s">
         <v>499</v>
@@ -51525,16 +51525,16 @@
     </row>
     <row r="935" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A935">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B935" t="s">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="C935" t="s">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="D935" t="s">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="E935" t="s">
         <v>499</v>
@@ -51552,7 +51552,7 @@
         <v>24</v>
       </c>
       <c r="J935">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K935">
         <v>0</v>
@@ -51563,16 +51563,16 @@
     </row>
     <row r="936" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A936">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B936" t="s">
-        <v>202</v>
+        <v>114</v>
       </c>
       <c r="C936" t="s">
-        <v>203</v>
+        <v>115</v>
       </c>
       <c r="D936" t="s">
-        <v>202</v>
+        <v>114</v>
       </c>
       <c r="E936" t="s">
         <v>499</v>
@@ -51590,7 +51590,7 @@
         <v>24</v>
       </c>
       <c r="J936">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K936">
         <v>0</v>
@@ -51601,16 +51601,16 @@
     </row>
     <row r="937" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A937">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B937" t="s">
-        <v>204</v>
+        <v>122</v>
       </c>
       <c r="C937" t="s">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="D937" t="s">
-        <v>204</v>
+        <v>122</v>
       </c>
       <c r="E937" t="s">
         <v>499</v>
@@ -51639,16 +51639,16 @@
     </row>
     <row r="938" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A938">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B938" t="s">
-        <v>240</v>
+        <v>142</v>
       </c>
       <c r="C938" t="s">
-        <v>241</v>
+        <v>143</v>
       </c>
       <c r="D938" t="s">
-        <v>240</v>
+        <v>142</v>
       </c>
       <c r="E938" t="s">
         <v>499</v>
@@ -51677,16 +51677,16 @@
     </row>
     <row r="939" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A939">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B939" t="s">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="C939" t="s">
-        <v>258</v>
+        <v>155</v>
       </c>
       <c r="D939" t="s">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="E939" t="s">
         <v>499</v>
@@ -51704,7 +51704,7 @@
         <v>24</v>
       </c>
       <c r="J939">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K939">
         <v>0</v>
@@ -51715,16 +51715,16 @@
     </row>
     <row r="940" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A940">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B940" t="s">
-        <v>273</v>
+        <v>174</v>
       </c>
       <c r="C940" t="s">
-        <v>274</v>
+        <v>175</v>
       </c>
       <c r="D940" t="s">
-        <v>273</v>
+        <v>174</v>
       </c>
       <c r="E940" t="s">
         <v>499</v>
@@ -51742,7 +51742,7 @@
         <v>24</v>
       </c>
       <c r="J940">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K940">
         <v>0</v>
@@ -51753,16 +51753,16 @@
     </row>
     <row r="941" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A941">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B941" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
       <c r="C941" t="s">
-        <v>298</v>
+        <v>181</v>
       </c>
       <c r="D941" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
       <c r="E941" t="s">
         <v>499</v>
@@ -51780,7 +51780,7 @@
         <v>24</v>
       </c>
       <c r="J941">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="K941">
         <v>0</v>
@@ -51791,16 +51791,16 @@
     </row>
     <row r="942" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A942">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B942" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="C942" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="D942" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="E942" t="s">
         <v>499</v>
@@ -51818,7 +51818,7 @@
         <v>24</v>
       </c>
       <c r="J942">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K942">
         <v>0</v>
@@ -51829,16 +51829,16 @@
     </row>
     <row r="943" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A943">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B943" t="s">
-        <v>307</v>
+        <v>198</v>
       </c>
       <c r="C943" t="s">
-        <v>308</v>
+        <v>199</v>
       </c>
       <c r="D943" t="s">
-        <v>307</v>
+        <v>198</v>
       </c>
       <c r="E943" t="s">
         <v>499</v>
@@ -51856,7 +51856,7 @@
         <v>24</v>
       </c>
       <c r="J943">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K943">
         <v>0</v>
@@ -51867,16 +51867,16 @@
     </row>
     <row r="944" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A944">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B944" t="s">
-        <v>311</v>
+        <v>202</v>
       </c>
       <c r="C944" t="s">
-        <v>312</v>
+        <v>203</v>
       </c>
       <c r="D944" t="s">
-        <v>311</v>
+        <v>202</v>
       </c>
       <c r="E944" t="s">
         <v>499</v>
@@ -51894,7 +51894,7 @@
         <v>24</v>
       </c>
       <c r="J944">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="K944">
         <v>0</v>
@@ -51908,13 +51908,13 @@
         <v>4604</v>
       </c>
       <c r="B945" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="C945" t="s">
-        <v>33</v>
+        <v>213</v>
       </c>
       <c r="D945" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="E945" t="s">
         <v>499</v>
@@ -51932,7 +51932,7 @@
         <v>24</v>
       </c>
       <c r="J945">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K945">
         <v>0</v>
@@ -51946,13 +51946,13 @@
         <v>4604</v>
       </c>
       <c r="B946" t="s">
-        <v>426</v>
+        <v>240</v>
       </c>
       <c r="C946" t="s">
-        <v>427</v>
+        <v>241</v>
       </c>
       <c r="D946" t="s">
-        <v>426</v>
+        <v>240</v>
       </c>
       <c r="E946" t="s">
         <v>499</v>
@@ -51970,7 +51970,7 @@
         <v>24</v>
       </c>
       <c r="J946">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K946">
         <v>0</v>
@@ -51984,13 +51984,13 @@
         <v>4604</v>
       </c>
       <c r="B947" t="s">
-        <v>52</v>
+        <v>257</v>
       </c>
       <c r="C947" t="s">
-        <v>53</v>
+        <v>258</v>
       </c>
       <c r="D947" t="s">
-        <v>52</v>
+        <v>257</v>
       </c>
       <c r="E947" t="s">
         <v>499</v>
@@ -52008,7 +52008,7 @@
         <v>24</v>
       </c>
       <c r="J947">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K947">
         <v>0</v>
@@ -52022,13 +52022,13 @@
         <v>4604</v>
       </c>
       <c r="B948" t="s">
-        <v>60</v>
+        <v>261</v>
       </c>
       <c r="C948" t="s">
-        <v>61</v>
+        <v>262</v>
       </c>
       <c r="D948" t="s">
-        <v>60</v>
+        <v>261</v>
       </c>
       <c r="E948" t="s">
         <v>499</v>
@@ -52046,7 +52046,7 @@
         <v>24</v>
       </c>
       <c r="J948">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K948">
         <v>0</v>
@@ -52060,13 +52060,13 @@
         <v>4604</v>
       </c>
       <c r="B949" t="s">
-        <v>567</v>
+        <v>263</v>
       </c>
       <c r="C949" t="s">
-        <v>568</v>
+        <v>264</v>
       </c>
       <c r="D949" t="s">
-        <v>567</v>
+        <v>263</v>
       </c>
       <c r="E949" t="s">
         <v>499</v>
@@ -52084,13 +52084,13 @@
         <v>24</v>
       </c>
       <c r="J949">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K949">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L949" t="s">
-        <v>569</v>
+        <v>25</v>
       </c>
     </row>
     <row r="950" spans="1:12" x14ac:dyDescent="0.25">
@@ -52098,13 +52098,13 @@
         <v>4604</v>
       </c>
       <c r="B950" t="s">
-        <v>578</v>
+        <v>273</v>
       </c>
       <c r="C950" t="s">
-        <v>579</v>
+        <v>274</v>
       </c>
       <c r="D950" t="s">
-        <v>578</v>
+        <v>273</v>
       </c>
       <c r="E950" t="s">
         <v>499</v>
@@ -52122,13 +52122,13 @@
         <v>24</v>
       </c>
       <c r="J950">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K950">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L950" t="s">
-        <v>580</v>
+        <v>25</v>
       </c>
     </row>
     <row r="951" spans="1:12" x14ac:dyDescent="0.25">
@@ -52136,13 +52136,13 @@
         <v>4604</v>
       </c>
       <c r="B951" t="s">
-        <v>581</v>
+        <v>275</v>
       </c>
       <c r="C951" t="s">
-        <v>582</v>
+        <v>276</v>
       </c>
       <c r="D951" t="s">
-        <v>581</v>
+        <v>275</v>
       </c>
       <c r="E951" t="s">
         <v>499</v>
@@ -52160,13 +52160,13 @@
         <v>24</v>
       </c>
       <c r="J951">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K951">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L951" t="s">
-        <v>580</v>
+        <v>25</v>
       </c>
     </row>
     <row r="952" spans="1:12" x14ac:dyDescent="0.25">
@@ -52174,13 +52174,13 @@
         <v>4604</v>
       </c>
       <c r="B952" t="s">
-        <v>583</v>
+        <v>281</v>
       </c>
       <c r="C952" t="s">
-        <v>584</v>
+        <v>282</v>
       </c>
       <c r="D952" t="s">
-        <v>583</v>
+        <v>281</v>
       </c>
       <c r="E952" t="s">
         <v>499</v>
@@ -52198,13 +52198,13 @@
         <v>24</v>
       </c>
       <c r="J952">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K952">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L952" t="s">
-        <v>585</v>
+        <v>25</v>
       </c>
     </row>
     <row r="953" spans="1:12" x14ac:dyDescent="0.25">
@@ -52212,13 +52212,13 @@
         <v>4604</v>
       </c>
       <c r="B953" t="s">
-        <v>586</v>
+        <v>289</v>
       </c>
       <c r="C953" t="s">
-        <v>587</v>
+        <v>290</v>
       </c>
       <c r="D953" t="s">
-        <v>586</v>
+        <v>289</v>
       </c>
       <c r="E953" t="s">
         <v>499</v>
@@ -52236,13 +52236,13 @@
         <v>24</v>
       </c>
       <c r="J953">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K953">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L953" t="s">
-        <v>585</v>
+        <v>25</v>
       </c>
     </row>
     <row r="954" spans="1:12" x14ac:dyDescent="0.25">
@@ -52250,13 +52250,13 @@
         <v>4604</v>
       </c>
       <c r="B954" t="s">
-        <v>780</v>
+        <v>397</v>
       </c>
       <c r="C954" t="s">
-        <v>781</v>
+        <v>398</v>
       </c>
       <c r="D954" t="s">
-        <v>780</v>
+        <v>397</v>
       </c>
       <c r="E954" t="s">
         <v>499</v>
@@ -52274,13 +52274,13 @@
         <v>24</v>
       </c>
       <c r="J954">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K954">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L954" t="s">
-        <v>566</v>
+        <v>25</v>
       </c>
     </row>
     <row r="955" spans="1:12" x14ac:dyDescent="0.25">
@@ -52288,13 +52288,13 @@
         <v>4604</v>
       </c>
       <c r="B955" t="s">
-        <v>611</v>
+        <v>309</v>
       </c>
       <c r="C955" t="s">
-        <v>612</v>
+        <v>310</v>
       </c>
       <c r="D955" t="s">
-        <v>611</v>
+        <v>309</v>
       </c>
       <c r="E955" t="s">
         <v>499</v>
@@ -52312,13 +52312,13 @@
         <v>24</v>
       </c>
       <c r="J955">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K955">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L955" t="s">
-        <v>566</v>
+        <v>25</v>
       </c>
     </row>
     <row r="956" spans="1:12" x14ac:dyDescent="0.25">
@@ -52326,13 +52326,13 @@
         <v>4604</v>
       </c>
       <c r="B956" t="s">
-        <v>613</v>
+        <v>347</v>
       </c>
       <c r="C956" t="s">
-        <v>614</v>
+        <v>348</v>
       </c>
       <c r="D956" t="s">
-        <v>613</v>
+        <v>347</v>
       </c>
       <c r="E956" t="s">
         <v>499</v>
@@ -52350,1647 +52350,13 @@
         <v>24</v>
       </c>
       <c r="J956">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K956">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L956" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="957" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A957">
-        <v>4604</v>
-      </c>
-      <c r="B957" t="s">
-        <v>615</v>
-      </c>
-      <c r="C957" t="s">
-        <v>616</v>
-      </c>
-      <c r="D957" t="s">
-        <v>615</v>
-      </c>
-      <c r="E957" t="s">
-        <v>499</v>
-      </c>
-      <c r="F957" t="s">
-        <v>24</v>
-      </c>
-      <c r="G957" t="s">
-        <v>22</v>
-      </c>
-      <c r="H957" t="s">
-        <v>23</v>
-      </c>
-      <c r="I957" t="s">
-        <v>24</v>
-      </c>
-      <c r="J957">
-        <v>0</v>
-      </c>
-      <c r="K957">
-        <v>8</v>
-      </c>
-      <c r="L957" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="958" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A958">
-        <v>4604</v>
-      </c>
-      <c r="B958" t="s">
-        <v>637</v>
-      </c>
-      <c r="C958" t="s">
-        <v>638</v>
-      </c>
-      <c r="D958" t="s">
-        <v>637</v>
-      </c>
-      <c r="E958" t="s">
-        <v>499</v>
-      </c>
-      <c r="F958" t="s">
-        <v>24</v>
-      </c>
-      <c r="G958" t="s">
-        <v>22</v>
-      </c>
-      <c r="H958" t="s">
-        <v>23</v>
-      </c>
-      <c r="I958" t="s">
-        <v>24</v>
-      </c>
-      <c r="J958">
-        <v>0</v>
-      </c>
-      <c r="K958">
-        <v>8</v>
-      </c>
-      <c r="L958" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="959" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A959">
-        <v>4604</v>
-      </c>
-      <c r="B959" t="s">
-        <v>66</v>
-      </c>
-      <c r="C959" t="s">
-        <v>67</v>
-      </c>
-      <c r="D959" t="s">
-        <v>66</v>
-      </c>
-      <c r="E959" t="s">
-        <v>499</v>
-      </c>
-      <c r="F959" t="s">
-        <v>24</v>
-      </c>
-      <c r="G959" t="s">
-        <v>22</v>
-      </c>
-      <c r="H959" t="s">
-        <v>23</v>
-      </c>
-      <c r="I959" t="s">
-        <v>24</v>
-      </c>
-      <c r="J959">
-        <v>12</v>
-      </c>
-      <c r="K959">
-        <v>0</v>
-      </c>
-      <c r="L959" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="960" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A960">
-        <v>4604</v>
-      </c>
-      <c r="B960" t="s">
-        <v>68</v>
-      </c>
-      <c r="C960" t="s">
-        <v>69</v>
-      </c>
-      <c r="D960" t="s">
-        <v>68</v>
-      </c>
-      <c r="E960" t="s">
-        <v>499</v>
-      </c>
-      <c r="F960" t="s">
-        <v>24</v>
-      </c>
-      <c r="G960" t="s">
-        <v>22</v>
-      </c>
-      <c r="H960" t="s">
-        <v>23</v>
-      </c>
-      <c r="I960" t="s">
-        <v>24</v>
-      </c>
-      <c r="J960">
-        <v>42</v>
-      </c>
-      <c r="K960">
-        <v>0</v>
-      </c>
-      <c r="L960" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="961" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A961">
-        <v>4604</v>
-      </c>
-      <c r="B961" t="s">
-        <v>70</v>
-      </c>
-      <c r="C961" t="s">
-        <v>71</v>
-      </c>
-      <c r="D961" t="s">
-        <v>70</v>
-      </c>
-      <c r="E961" t="s">
-        <v>499</v>
-      </c>
-      <c r="F961" t="s">
-        <v>24</v>
-      </c>
-      <c r="G961" t="s">
-        <v>22</v>
-      </c>
-      <c r="H961" t="s">
-        <v>23</v>
-      </c>
-      <c r="I961" t="s">
-        <v>24</v>
-      </c>
-      <c r="J961">
-        <v>186</v>
-      </c>
-      <c r="K961">
-        <v>0</v>
-      </c>
-      <c r="L961" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="962" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A962">
-        <v>4604</v>
-      </c>
-      <c r="B962" t="s">
-        <v>78</v>
-      </c>
-      <c r="C962" t="s">
-        <v>79</v>
-      </c>
-      <c r="D962" t="s">
-        <v>78</v>
-      </c>
-      <c r="E962" t="s">
-        <v>499</v>
-      </c>
-      <c r="F962" t="s">
-        <v>24</v>
-      </c>
-      <c r="G962" t="s">
-        <v>22</v>
-      </c>
-      <c r="H962" t="s">
-        <v>23</v>
-      </c>
-      <c r="I962" t="s">
-        <v>24</v>
-      </c>
-      <c r="J962">
-        <v>12</v>
-      </c>
-      <c r="K962">
-        <v>0</v>
-      </c>
-      <c r="L962" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="963" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A963">
-        <v>4604</v>
-      </c>
-      <c r="B963" t="s">
-        <v>98</v>
-      </c>
-      <c r="C963" t="s">
-        <v>99</v>
-      </c>
-      <c r="D963" t="s">
-        <v>98</v>
-      </c>
-      <c r="E963" t="s">
-        <v>499</v>
-      </c>
-      <c r="F963" t="s">
-        <v>24</v>
-      </c>
-      <c r="G963" t="s">
-        <v>22</v>
-      </c>
-      <c r="H963" t="s">
-        <v>23</v>
-      </c>
-      <c r="I963" t="s">
-        <v>24</v>
-      </c>
-      <c r="J963">
-        <v>2</v>
-      </c>
-      <c r="K963">
-        <v>0</v>
-      </c>
-      <c r="L963" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="964" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A964">
-        <v>4604</v>
-      </c>
-      <c r="B964" t="s">
-        <v>100</v>
-      </c>
-      <c r="C964" t="s">
-        <v>101</v>
-      </c>
-      <c r="D964" t="s">
-        <v>100</v>
-      </c>
-      <c r="E964" t="s">
-        <v>499</v>
-      </c>
-      <c r="F964" t="s">
-        <v>24</v>
-      </c>
-      <c r="G964" t="s">
-        <v>22</v>
-      </c>
-      <c r="H964" t="s">
-        <v>23</v>
-      </c>
-      <c r="I964" t="s">
-        <v>24</v>
-      </c>
-      <c r="J964">
-        <v>90</v>
-      </c>
-      <c r="K964">
-        <v>0</v>
-      </c>
-      <c r="L964" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="965" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A965">
-        <v>4604</v>
-      </c>
-      <c r="B965" t="s">
-        <v>379</v>
-      </c>
-      <c r="C965" t="s">
-        <v>380</v>
-      </c>
-      <c r="D965" t="s">
-        <v>379</v>
-      </c>
-      <c r="E965" t="s">
-        <v>499</v>
-      </c>
-      <c r="F965" t="s">
-        <v>24</v>
-      </c>
-      <c r="G965" t="s">
-        <v>22</v>
-      </c>
-      <c r="H965" t="s">
-        <v>23</v>
-      </c>
-      <c r="I965" t="s">
-        <v>24</v>
-      </c>
-      <c r="J965">
-        <v>6</v>
-      </c>
-      <c r="K965">
-        <v>0</v>
-      </c>
-      <c r="L965" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="966" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A966">
-        <v>4604</v>
-      </c>
-      <c r="B966" t="s">
-        <v>102</v>
-      </c>
-      <c r="C966" t="s">
-        <v>103</v>
-      </c>
-      <c r="D966" t="s">
-        <v>102</v>
-      </c>
-      <c r="E966" t="s">
-        <v>499</v>
-      </c>
-      <c r="F966" t="s">
-        <v>24</v>
-      </c>
-      <c r="G966" t="s">
-        <v>22</v>
-      </c>
-      <c r="H966" t="s">
-        <v>23</v>
-      </c>
-      <c r="I966" t="s">
-        <v>24</v>
-      </c>
-      <c r="J966">
-        <v>1</v>
-      </c>
-      <c r="K966">
-        <v>0</v>
-      </c>
-      <c r="L966" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="967" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A967">
-        <v>4604</v>
-      </c>
-      <c r="B967" t="s">
-        <v>106</v>
-      </c>
-      <c r="C967" t="s">
-        <v>107</v>
-      </c>
-      <c r="D967" t="s">
-        <v>106</v>
-      </c>
-      <c r="E967" t="s">
-        <v>499</v>
-      </c>
-      <c r="F967" t="s">
-        <v>24</v>
-      </c>
-      <c r="G967" t="s">
-        <v>22</v>
-      </c>
-      <c r="H967" t="s">
-        <v>23</v>
-      </c>
-      <c r="I967" t="s">
-        <v>24</v>
-      </c>
-      <c r="J967">
-        <v>24</v>
-      </c>
-      <c r="K967">
-        <v>0</v>
-      </c>
-      <c r="L967" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="968" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A968">
-        <v>4604</v>
-      </c>
-      <c r="B968" t="s">
-        <v>110</v>
-      </c>
-      <c r="C968" t="s">
-        <v>111</v>
-      </c>
-      <c r="D968" t="s">
-        <v>110</v>
-      </c>
-      <c r="E968" t="s">
-        <v>499</v>
-      </c>
-      <c r="F968" t="s">
-        <v>24</v>
-      </c>
-      <c r="G968" t="s">
-        <v>22</v>
-      </c>
-      <c r="H968" t="s">
-        <v>23</v>
-      </c>
-      <c r="I968" t="s">
-        <v>24</v>
-      </c>
-      <c r="J968">
-        <v>6</v>
-      </c>
-      <c r="K968">
-        <v>0</v>
-      </c>
-      <c r="L968" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="969" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A969">
-        <v>4604</v>
-      </c>
-      <c r="B969" t="s">
-        <v>114</v>
-      </c>
-      <c r="C969" t="s">
-        <v>115</v>
-      </c>
-      <c r="D969" t="s">
-        <v>114</v>
-      </c>
-      <c r="E969" t="s">
-        <v>499</v>
-      </c>
-      <c r="F969" t="s">
-        <v>24</v>
-      </c>
-      <c r="G969" t="s">
-        <v>22</v>
-      </c>
-      <c r="H969" t="s">
-        <v>23</v>
-      </c>
-      <c r="I969" t="s">
-        <v>24</v>
-      </c>
-      <c r="J969">
-        <v>30</v>
-      </c>
-      <c r="K969">
-        <v>0</v>
-      </c>
-      <c r="L969" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="970" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A970">
-        <v>4604</v>
-      </c>
-      <c r="B970" t="s">
-        <v>122</v>
-      </c>
-      <c r="C970" t="s">
-        <v>123</v>
-      </c>
-      <c r="D970" t="s">
-        <v>122</v>
-      </c>
-      <c r="E970" t="s">
-        <v>499</v>
-      </c>
-      <c r="F970" t="s">
-        <v>24</v>
-      </c>
-      <c r="G970" t="s">
-        <v>22</v>
-      </c>
-      <c r="H970" t="s">
-        <v>23</v>
-      </c>
-      <c r="I970" t="s">
-        <v>24</v>
-      </c>
-      <c r="J970">
-        <v>6</v>
-      </c>
-      <c r="K970">
-        <v>0</v>
-      </c>
-      <c r="L970" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="971" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A971">
-        <v>4604</v>
-      </c>
-      <c r="B971" t="s">
-        <v>142</v>
-      </c>
-      <c r="C971" t="s">
-        <v>143</v>
-      </c>
-      <c r="D971" t="s">
-        <v>142</v>
-      </c>
-      <c r="E971" t="s">
-        <v>499</v>
-      </c>
-      <c r="F971" t="s">
-        <v>24</v>
-      </c>
-      <c r="G971" t="s">
-        <v>22</v>
-      </c>
-      <c r="H971" t="s">
-        <v>23</v>
-      </c>
-      <c r="I971" t="s">
-        <v>24</v>
-      </c>
-      <c r="J971">
-        <v>6</v>
-      </c>
-      <c r="K971">
-        <v>0</v>
-      </c>
-      <c r="L971" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="972" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A972">
-        <v>4604</v>
-      </c>
-      <c r="B972" t="s">
-        <v>154</v>
-      </c>
-      <c r="C972" t="s">
-        <v>155</v>
-      </c>
-      <c r="D972" t="s">
-        <v>154</v>
-      </c>
-      <c r="E972" t="s">
-        <v>499</v>
-      </c>
-      <c r="F972" t="s">
-        <v>24</v>
-      </c>
-      <c r="G972" t="s">
-        <v>22</v>
-      </c>
-      <c r="H972" t="s">
-        <v>23</v>
-      </c>
-      <c r="I972" t="s">
-        <v>24</v>
-      </c>
-      <c r="J972">
-        <v>6</v>
-      </c>
-      <c r="K972">
-        <v>0</v>
-      </c>
-      <c r="L972" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="973" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A973">
-        <v>4604</v>
-      </c>
-      <c r="B973" t="s">
-        <v>174</v>
-      </c>
-      <c r="C973" t="s">
-        <v>175</v>
-      </c>
-      <c r="D973" t="s">
-        <v>174</v>
-      </c>
-      <c r="E973" t="s">
-        <v>499</v>
-      </c>
-      <c r="F973" t="s">
-        <v>24</v>
-      </c>
-      <c r="G973" t="s">
-        <v>22</v>
-      </c>
-      <c r="H973" t="s">
-        <v>23</v>
-      </c>
-      <c r="I973" t="s">
-        <v>24</v>
-      </c>
-      <c r="J973">
-        <v>18</v>
-      </c>
-      <c r="K973">
-        <v>0</v>
-      </c>
-      <c r="L973" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="974" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A974">
-        <v>4604</v>
-      </c>
-      <c r="B974" t="s">
-        <v>180</v>
-      </c>
-      <c r="C974" t="s">
-        <v>181</v>
-      </c>
-      <c r="D974" t="s">
-        <v>180</v>
-      </c>
-      <c r="E974" t="s">
-        <v>499</v>
-      </c>
-      <c r="F974" t="s">
-        <v>24</v>
-      </c>
-      <c r="G974" t="s">
-        <v>22</v>
-      </c>
-      <c r="H974" t="s">
-        <v>23</v>
-      </c>
-      <c r="I974" t="s">
-        <v>24</v>
-      </c>
-      <c r="J974">
-        <v>36</v>
-      </c>
-      <c r="K974">
-        <v>0</v>
-      </c>
-      <c r="L974" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="975" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A975">
-        <v>4604</v>
-      </c>
-      <c r="B975" t="s">
-        <v>353</v>
-      </c>
-      <c r="C975" t="s">
-        <v>354</v>
-      </c>
-      <c r="D975" t="s">
-        <v>353</v>
-      </c>
-      <c r="E975" t="s">
-        <v>499</v>
-      </c>
-      <c r="F975" t="s">
-        <v>24</v>
-      </c>
-      <c r="G975" t="s">
-        <v>22</v>
-      </c>
-      <c r="H975" t="s">
-        <v>23</v>
-      </c>
-      <c r="I975" t="s">
-        <v>24</v>
-      </c>
-      <c r="J975">
-        <v>12</v>
-      </c>
-      <c r="K975">
-        <v>0</v>
-      </c>
-      <c r="L975" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="976" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A976">
-        <v>4604</v>
-      </c>
-      <c r="B976" t="s">
-        <v>198</v>
-      </c>
-      <c r="C976" t="s">
-        <v>199</v>
-      </c>
-      <c r="D976" t="s">
-        <v>198</v>
-      </c>
-      <c r="E976" t="s">
-        <v>499</v>
-      </c>
-      <c r="F976" t="s">
-        <v>24</v>
-      </c>
-      <c r="G976" t="s">
-        <v>22</v>
-      </c>
-      <c r="H976" t="s">
-        <v>23</v>
-      </c>
-      <c r="I976" t="s">
-        <v>24</v>
-      </c>
-      <c r="J976">
-        <v>12</v>
-      </c>
-      <c r="K976">
-        <v>0</v>
-      </c>
-      <c r="L976" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="977" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A977">
-        <v>4604</v>
-      </c>
-      <c r="B977" t="s">
-        <v>202</v>
-      </c>
-      <c r="C977" t="s">
-        <v>203</v>
-      </c>
-      <c r="D977" t="s">
-        <v>202</v>
-      </c>
-      <c r="E977" t="s">
-        <v>499</v>
-      </c>
-      <c r="F977" t="s">
-        <v>24</v>
-      </c>
-      <c r="G977" t="s">
-        <v>22</v>
-      </c>
-      <c r="H977" t="s">
-        <v>23</v>
-      </c>
-      <c r="I977" t="s">
-        <v>24</v>
-      </c>
-      <c r="J977">
-        <v>6</v>
-      </c>
-      <c r="K977">
-        <v>0</v>
-      </c>
-      <c r="L977" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="978" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A978">
-        <v>4604</v>
-      </c>
-      <c r="B978" t="s">
-        <v>212</v>
-      </c>
-      <c r="C978" t="s">
-        <v>213</v>
-      </c>
-      <c r="D978" t="s">
-        <v>212</v>
-      </c>
-      <c r="E978" t="s">
-        <v>499</v>
-      </c>
-      <c r="F978" t="s">
-        <v>24</v>
-      </c>
-      <c r="G978" t="s">
-        <v>22</v>
-      </c>
-      <c r="H978" t="s">
-        <v>23</v>
-      </c>
-      <c r="I978" t="s">
-        <v>24</v>
-      </c>
-      <c r="J978">
-        <v>12</v>
-      </c>
-      <c r="K978">
-        <v>0</v>
-      </c>
-      <c r="L978" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="979" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A979">
-        <v>4604</v>
-      </c>
-      <c r="B979" t="s">
-        <v>240</v>
-      </c>
-      <c r="C979" t="s">
-        <v>241</v>
-      </c>
-      <c r="D979" t="s">
-        <v>240</v>
-      </c>
-      <c r="E979" t="s">
-        <v>499</v>
-      </c>
-      <c r="F979" t="s">
-        <v>24</v>
-      </c>
-      <c r="G979" t="s">
-        <v>22</v>
-      </c>
-      <c r="H979" t="s">
-        <v>23</v>
-      </c>
-      <c r="I979" t="s">
-        <v>24</v>
-      </c>
-      <c r="J979">
-        <v>6</v>
-      </c>
-      <c r="K979">
-        <v>0</v>
-      </c>
-      <c r="L979" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="980" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A980">
-        <v>4604</v>
-      </c>
-      <c r="B980" t="s">
-        <v>257</v>
-      </c>
-      <c r="C980" t="s">
-        <v>258</v>
-      </c>
-      <c r="D980" t="s">
-        <v>257</v>
-      </c>
-      <c r="E980" t="s">
-        <v>499</v>
-      </c>
-      <c r="F980" t="s">
-        <v>24</v>
-      </c>
-      <c r="G980" t="s">
-        <v>22</v>
-      </c>
-      <c r="H980" t="s">
-        <v>23</v>
-      </c>
-      <c r="I980" t="s">
-        <v>24</v>
-      </c>
-      <c r="J980">
-        <v>18</v>
-      </c>
-      <c r="K980">
-        <v>0</v>
-      </c>
-      <c r="L980" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="981" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A981">
-        <v>4604</v>
-      </c>
-      <c r="B981" t="s">
-        <v>261</v>
-      </c>
-      <c r="C981" t="s">
-        <v>262</v>
-      </c>
-      <c r="D981" t="s">
-        <v>261</v>
-      </c>
-      <c r="E981" t="s">
-        <v>499</v>
-      </c>
-      <c r="F981" t="s">
-        <v>24</v>
-      </c>
-      <c r="G981" t="s">
-        <v>22</v>
-      </c>
-      <c r="H981" t="s">
-        <v>23</v>
-      </c>
-      <c r="I981" t="s">
-        <v>24</v>
-      </c>
-      <c r="J981">
-        <v>3</v>
-      </c>
-      <c r="K981">
-        <v>0</v>
-      </c>
-      <c r="L981" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="982" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A982">
-        <v>4604</v>
-      </c>
-      <c r="B982" t="s">
-        <v>263</v>
-      </c>
-      <c r="C982" t="s">
-        <v>264</v>
-      </c>
-      <c r="D982" t="s">
-        <v>263</v>
-      </c>
-      <c r="E982" t="s">
-        <v>499</v>
-      </c>
-      <c r="F982" t="s">
-        <v>24</v>
-      </c>
-      <c r="G982" t="s">
-        <v>22</v>
-      </c>
-      <c r="H982" t="s">
-        <v>23</v>
-      </c>
-      <c r="I982" t="s">
-        <v>24</v>
-      </c>
-      <c r="J982">
-        <v>3</v>
-      </c>
-      <c r="K982">
-        <v>0</v>
-      </c>
-      <c r="L982" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="983" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A983">
-        <v>4604</v>
-      </c>
-      <c r="B983" t="s">
-        <v>273</v>
-      </c>
-      <c r="C983" t="s">
-        <v>274</v>
-      </c>
-      <c r="D983" t="s">
-        <v>273</v>
-      </c>
-      <c r="E983" t="s">
-        <v>499</v>
-      </c>
-      <c r="F983" t="s">
-        <v>24</v>
-      </c>
-      <c r="G983" t="s">
-        <v>22</v>
-      </c>
-      <c r="H983" t="s">
-        <v>23</v>
-      </c>
-      <c r="I983" t="s">
-        <v>24</v>
-      </c>
-      <c r="J983">
-        <v>12</v>
-      </c>
-      <c r="K983">
-        <v>0</v>
-      </c>
-      <c r="L983" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="984" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A984">
-        <v>4604</v>
-      </c>
-      <c r="B984" t="s">
-        <v>275</v>
-      </c>
-      <c r="C984" t="s">
-        <v>276</v>
-      </c>
-      <c r="D984" t="s">
-        <v>275</v>
-      </c>
-      <c r="E984" t="s">
-        <v>499</v>
-      </c>
-      <c r="F984" t="s">
-        <v>24</v>
-      </c>
-      <c r="G984" t="s">
-        <v>22</v>
-      </c>
-      <c r="H984" t="s">
-        <v>23</v>
-      </c>
-      <c r="I984" t="s">
-        <v>24</v>
-      </c>
-      <c r="J984">
-        <v>3</v>
-      </c>
-      <c r="K984">
-        <v>0</v>
-      </c>
-      <c r="L984" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="985" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A985">
-        <v>4604</v>
-      </c>
-      <c r="B985" t="s">
-        <v>281</v>
-      </c>
-      <c r="C985" t="s">
-        <v>282</v>
-      </c>
-      <c r="D985" t="s">
-        <v>281</v>
-      </c>
-      <c r="E985" t="s">
-        <v>499</v>
-      </c>
-      <c r="F985" t="s">
-        <v>24</v>
-      </c>
-      <c r="G985" t="s">
-        <v>22</v>
-      </c>
-      <c r="H985" t="s">
-        <v>23</v>
-      </c>
-      <c r="I985" t="s">
-        <v>24</v>
-      </c>
-      <c r="J985">
-        <v>3</v>
-      </c>
-      <c r="K985">
-        <v>0</v>
-      </c>
-      <c r="L985" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="986" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A986">
-        <v>4604</v>
-      </c>
-      <c r="B986" t="s">
-        <v>289</v>
-      </c>
-      <c r="C986" t="s">
-        <v>290</v>
-      </c>
-      <c r="D986" t="s">
-        <v>289</v>
-      </c>
-      <c r="E986" t="s">
-        <v>499</v>
-      </c>
-      <c r="F986" t="s">
-        <v>24</v>
-      </c>
-      <c r="G986" t="s">
-        <v>22</v>
-      </c>
-      <c r="H986" t="s">
-        <v>23</v>
-      </c>
-      <c r="I986" t="s">
-        <v>24</v>
-      </c>
-      <c r="J986">
-        <v>3</v>
-      </c>
-      <c r="K986">
-        <v>0</v>
-      </c>
-      <c r="L986" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="987" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A987">
-        <v>4604</v>
-      </c>
-      <c r="B987" t="s">
-        <v>397</v>
-      </c>
-      <c r="C987" t="s">
-        <v>398</v>
-      </c>
-      <c r="D987" t="s">
-        <v>397</v>
-      </c>
-      <c r="E987" t="s">
-        <v>499</v>
-      </c>
-      <c r="F987" t="s">
-        <v>24</v>
-      </c>
-      <c r="G987" t="s">
-        <v>22</v>
-      </c>
-      <c r="H987" t="s">
-        <v>23</v>
-      </c>
-      <c r="I987" t="s">
-        <v>24</v>
-      </c>
-      <c r="J987">
-        <v>3</v>
-      </c>
-      <c r="K987">
-        <v>0</v>
-      </c>
-      <c r="L987" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="988" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A988">
-        <v>4604</v>
-      </c>
-      <c r="B988" t="s">
-        <v>309</v>
-      </c>
-      <c r="C988" t="s">
-        <v>310</v>
-      </c>
-      <c r="D988" t="s">
-        <v>309</v>
-      </c>
-      <c r="E988" t="s">
-        <v>499</v>
-      </c>
-      <c r="F988" t="s">
-        <v>24</v>
-      </c>
-      <c r="G988" t="s">
-        <v>22</v>
-      </c>
-      <c r="H988" t="s">
-        <v>23</v>
-      </c>
-      <c r="I988" t="s">
-        <v>24</v>
-      </c>
-      <c r="J988">
-        <v>6</v>
-      </c>
-      <c r="K988">
-        <v>0</v>
-      </c>
-      <c r="L988" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="989" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A989">
-        <v>4604</v>
-      </c>
-      <c r="B989" t="s">
-        <v>347</v>
-      </c>
-      <c r="C989" t="s">
-        <v>348</v>
-      </c>
-      <c r="D989" t="s">
-        <v>347</v>
-      </c>
-      <c r="E989" t="s">
-        <v>499</v>
-      </c>
-      <c r="F989" t="s">
-        <v>24</v>
-      </c>
-      <c r="G989" t="s">
-        <v>22</v>
-      </c>
-      <c r="H989" t="s">
-        <v>23</v>
-      </c>
-      <c r="I989" t="s">
-        <v>24</v>
-      </c>
-      <c r="J989">
-        <v>6</v>
-      </c>
-      <c r="K989">
-        <v>0</v>
-      </c>
-      <c r="L989" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="990" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A990">
-        <v>4605</v>
-      </c>
-      <c r="B990" t="s">
-        <v>112</v>
-      </c>
-      <c r="C990" t="s">
-        <v>113</v>
-      </c>
-      <c r="D990" t="s">
-        <v>112</v>
-      </c>
-      <c r="E990" t="s">
-        <v>499</v>
-      </c>
-      <c r="F990" t="s">
-        <v>24</v>
-      </c>
-      <c r="G990" t="s">
-        <v>22</v>
-      </c>
-      <c r="H990" t="s">
-        <v>23</v>
-      </c>
-      <c r="I990" t="s">
-        <v>24</v>
-      </c>
-      <c r="J990">
-        <v>3630</v>
-      </c>
-      <c r="K990">
-        <v>0</v>
-      </c>
-      <c r="L990" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="991" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A991">
-        <v>4605</v>
-      </c>
-      <c r="B991" t="s">
-        <v>114</v>
-      </c>
-      <c r="C991" t="s">
-        <v>115</v>
-      </c>
-      <c r="D991" t="s">
-        <v>114</v>
-      </c>
-      <c r="E991" t="s">
-        <v>499</v>
-      </c>
-      <c r="F991" t="s">
-        <v>24</v>
-      </c>
-      <c r="G991" t="s">
-        <v>22</v>
-      </c>
-      <c r="H991" t="s">
-        <v>23</v>
-      </c>
-      <c r="I991" t="s">
-        <v>24</v>
-      </c>
-      <c r="J991">
-        <v>3612</v>
-      </c>
-      <c r="K991">
-        <v>0</v>
-      </c>
-      <c r="L991" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="992" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A992">
-        <v>4606</v>
-      </c>
-      <c r="B992" t="s">
-        <v>545</v>
-      </c>
-      <c r="C992" t="s">
-        <v>546</v>
-      </c>
-      <c r="D992" t="s">
-        <v>545</v>
-      </c>
-      <c r="E992" t="s">
-        <v>499</v>
-      </c>
-      <c r="F992" t="s">
-        <v>24</v>
-      </c>
-      <c r="G992" t="s">
-        <v>22</v>
-      </c>
-      <c r="H992" t="s">
-        <v>23</v>
-      </c>
-      <c r="I992" t="s">
-        <v>24</v>
-      </c>
-      <c r="J992">
-        <v>2</v>
-      </c>
-      <c r="K992">
-        <v>17</v>
-      </c>
-      <c r="L992" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="993" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A993">
-        <v>4606</v>
-      </c>
-      <c r="B993" t="s">
-        <v>551</v>
-      </c>
-      <c r="C993" t="s">
-        <v>552</v>
-      </c>
-      <c r="D993" t="s">
-        <v>551</v>
-      </c>
-      <c r="E993" t="s">
-        <v>499</v>
-      </c>
-      <c r="F993" t="s">
-        <v>24</v>
-      </c>
-      <c r="G993" t="s">
-        <v>22</v>
-      </c>
-      <c r="H993" t="s">
-        <v>23</v>
-      </c>
-      <c r="I993" t="s">
-        <v>24</v>
-      </c>
-      <c r="J993">
-        <v>2</v>
-      </c>
-      <c r="K993">
-        <v>28</v>
-      </c>
-      <c r="L993" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="994" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A994">
-        <v>4607</v>
-      </c>
-      <c r="B994" t="s">
-        <v>545</v>
-      </c>
-      <c r="C994" t="s">
-        <v>546</v>
-      </c>
-      <c r="D994" t="s">
-        <v>545</v>
-      </c>
-      <c r="E994" t="s">
-        <v>499</v>
-      </c>
-      <c r="F994" t="s">
-        <v>24</v>
-      </c>
-      <c r="G994" t="s">
-        <v>22</v>
-      </c>
-      <c r="H994" t="s">
-        <v>23</v>
-      </c>
-      <c r="I994" t="s">
-        <v>24</v>
-      </c>
-      <c r="J994">
-        <v>3</v>
-      </c>
-      <c r="K994">
-        <v>26</v>
-      </c>
-      <c r="L994" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="995" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A995">
-        <v>4607</v>
-      </c>
-      <c r="B995" t="s">
-        <v>551</v>
-      </c>
-      <c r="C995" t="s">
-        <v>552</v>
-      </c>
-      <c r="D995" t="s">
-        <v>551</v>
-      </c>
-      <c r="E995" t="s">
-        <v>499</v>
-      </c>
-      <c r="F995" t="s">
-        <v>24</v>
-      </c>
-      <c r="G995" t="s">
-        <v>22</v>
-      </c>
-      <c r="H995" t="s">
-        <v>23</v>
-      </c>
-      <c r="I995" t="s">
-        <v>24</v>
-      </c>
-      <c r="J995">
-        <v>1</v>
-      </c>
-      <c r="K995">
-        <v>50</v>
-      </c>
-      <c r="L995" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="996" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A996">
-        <v>4608</v>
-      </c>
-      <c r="B996" t="s">
-        <v>545</v>
-      </c>
-      <c r="C996" t="s">
-        <v>546</v>
-      </c>
-      <c r="D996" t="s">
-        <v>545</v>
-      </c>
-      <c r="E996" t="s">
-        <v>499</v>
-      </c>
-      <c r="F996" t="s">
-        <v>24</v>
-      </c>
-      <c r="G996" t="s">
-        <v>22</v>
-      </c>
-      <c r="H996" t="s">
-        <v>23</v>
-      </c>
-      <c r="I996" t="s">
-        <v>24</v>
-      </c>
-      <c r="J996">
-        <v>3</v>
-      </c>
-      <c r="K996">
-        <v>6</v>
-      </c>
-      <c r="L996" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="997" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A997">
-        <v>4608</v>
-      </c>
-      <c r="B997" t="s">
-        <v>551</v>
-      </c>
-      <c r="C997" t="s">
-        <v>552</v>
-      </c>
-      <c r="D997" t="s">
-        <v>551</v>
-      </c>
-      <c r="E997" t="s">
-        <v>499</v>
-      </c>
-      <c r="F997" t="s">
-        <v>24</v>
-      </c>
-      <c r="G997" t="s">
-        <v>22</v>
-      </c>
-      <c r="H997" t="s">
-        <v>23</v>
-      </c>
-      <c r="I997" t="s">
-        <v>24</v>
-      </c>
-      <c r="J997">
-        <v>2</v>
-      </c>
-      <c r="K997">
-        <v>0</v>
-      </c>
-      <c r="L997" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="998" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A998">
-        <v>4609</v>
-      </c>
-      <c r="B998" t="s">
-        <v>545</v>
-      </c>
-      <c r="C998" t="s">
-        <v>546</v>
-      </c>
-      <c r="D998" t="s">
-        <v>545</v>
-      </c>
-      <c r="E998" t="s">
-        <v>499</v>
-      </c>
-      <c r="F998" t="s">
-        <v>24</v>
-      </c>
-      <c r="G998" t="s">
-        <v>22</v>
-      </c>
-      <c r="H998" t="s">
-        <v>23</v>
-      </c>
-      <c r="I998" t="s">
-        <v>24</v>
-      </c>
-      <c r="J998">
-        <v>2</v>
-      </c>
-      <c r="K998">
-        <v>29</v>
-      </c>
-      <c r="L998" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="999" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A999">
-        <v>4609</v>
-      </c>
-      <c r="B999" t="s">
-        <v>551</v>
-      </c>
-      <c r="C999" t="s">
-        <v>552</v>
-      </c>
-      <c r="D999" t="s">
-        <v>551</v>
-      </c>
-      <c r="E999" t="s">
-        <v>499</v>
-      </c>
-      <c r="F999" t="s">
-        <v>24</v>
-      </c>
-      <c r="G999" t="s">
-        <v>22</v>
-      </c>
-      <c r="H999" t="s">
-        <v>23</v>
-      </c>
-      <c r="I999" t="s">
-        <v>24</v>
-      </c>
-      <c r="J999">
-        <v>2</v>
-      </c>
-      <c r="K999">
-        <v>25</v>
-      </c>
-      <c r="L999" t="s">
-        <v>550</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
